--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513660_FASEFINALBFFB3_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513660_FASEFINALBFFB3_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3063</v>
+        <v>4.994</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2257</v>
+        <v>2.8855</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0806</v>
+        <v>2.1085</v>
       </c>
       <c r="G2" t="n">
         <v>3.5399</v>
@@ -610,13 +610,13 @@
         <v>1.5579</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7078</v>
+        <v>-0.0201</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.042</v>
+        <v>-0.3821</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3342</v>
+        <v>0.362</v>
       </c>
       <c r="V2" t="n">
         <v>0.89</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. MONTERO ISLA</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6058</v>
+        <v>4.5844</v>
       </c>
       <c r="E3" t="n">
-        <v>1.949</v>
+        <v>5.9012</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6568</v>
+        <v>-1.3168</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9858</v>
+        <v>4.0285</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5024</v>
+        <v>1.0719</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4882</v>
+        <v>2.9566</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3463</v>
+        <v>4.6349</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6235000000000001</v>
+        <v>2.0244</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9697</v>
+        <v>2.6104</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6395999999999999</v>
+        <v>-0.6063</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1211</v>
+        <v>-0.9525</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5185</v>
+        <v>0.3462</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9737</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.921</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9737</v>
+        <v>1.3632</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5748</v>
+        <v>-0.5563</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6183</v>
+        <v>0.2963</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0435</v>
+        <v>-0.8526</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2211</v>
+        <v>2.67</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2211</v>
+        <v>3.8911</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>I. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3016</v>
+        <v>3.7525</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9801</v>
+        <v>2.272</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6785</v>
+        <v>1.4806</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0285</v>
+        <v>1.9858</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0719</v>
+        <v>-0.5024</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9566</v>
+        <v>2.4882</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6349</v>
+        <v>1.3463</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0244</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6104</v>
+        <v>1.9697</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6063</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9525</v>
+        <v>0.1211</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3462</v>
+        <v>0.5185</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5579</v>
+        <v>0.9737</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.921</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3632</v>
+        <v>0.9737</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.8391</v>
+        <v>-0.428</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6248</v>
+        <v>-0.2953</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2143</v>
+        <v>-0.1327</v>
       </c>
       <c r="V4" t="n">
-        <v>2.67</v>
+        <v>1.2211</v>
       </c>
       <c r="W4" t="n">
-        <v>3.8911</v>
+        <v>1.2211</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>M. LAGUNA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2967</v>
+        <v>1.7842</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4889</v>
+        <v>1.3825</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.1921</v>
+        <v>0.4016</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.9661</v>
+        <v>1.3771</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.9023</v>
+        <v>-0.6266</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0638</v>
+        <v>2.0037</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.3715</v>
+        <v>1.2941</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.6957</v>
+        <v>-0.6029</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3242</v>
+        <v>1.897</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5946</v>
+        <v>0.083</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2065</v>
+        <v>-0.0236</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3881</v>
+        <v>0.1067</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3895</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.5842000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>5.3134</v>
+        <v>-0.4566</v>
       </c>
       <c r="T5" t="n">
-        <v>4.2741</v>
+        <v>-0.191</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0393</v>
+        <v>-0.2656</v>
       </c>
       <c r="V5" t="n">
-        <v>2.339</v>
+        <v>0.2795</v>
       </c>
       <c r="W5" t="n">
-        <v>3.56</v>
+        <v>0.2795</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. LAGUNA RODRIGUEZ</t>
+          <t>V. NEGRE FABREGAT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9441</v>
+        <v>0.8535</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6816</v>
+        <v>1.1946</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2625</v>
+        <v>-0.3411</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3771</v>
+        <v>2.1966</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6266</v>
+        <v>0.3371</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0037</v>
+        <v>1.8595</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2941</v>
+        <v>3.4373</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6029</v>
+        <v>0.3489</v>
       </c>
       <c r="L6" t="n">
-        <v>1.897</v>
+        <v>3.0884</v>
       </c>
       <c r="M6" t="n">
-        <v>0.083</v>
+        <v>-1.2407</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0236</v>
+        <v>-0.0118</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1067</v>
+        <v>-1.2289</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5842000000000001</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.7789</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2967</v>
+        <v>-0.1747</v>
       </c>
       <c r="T6" t="n">
-        <v>0.108</v>
+        <v>-0.2953</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4047</v>
+        <v>0.1207</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8683</v>
+        <v>0.6311</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07539999999999999</v>
+        <v>-0.1618</v>
       </c>
       <c r="F7" t="n">
         <v>0.7929</v>
@@ -1000,10 +1000,10 @@
         <v>1.5579</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2843</v>
+        <v>-0.5215</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1393</v>
+        <v>-0.3765</v>
       </c>
       <c r="U7" t="n">
         <v>-0.1449</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. NEGRE FABREGAT</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3975</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9334</v>
+        <v>2.9213</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5359</v>
+        <v>-2.9991</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1966</v>
+        <v>-3.9661</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3371</v>
+        <v>-2.9023</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8595</v>
+        <v>-1.0638</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4373</v>
+        <v>-1.3715</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3489</v>
+        <v>-1.6957</v>
       </c>
       <c r="L8" t="n">
-        <v>3.0884</v>
+        <v>0.3242</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2407</v>
+        <v>-2.5946</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0118</v>
+        <v>-1.2065</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2289</v>
+        <v>-1.3881</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1684</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9474</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7789</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6306</v>
+        <v>1.9388</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5565</v>
+        <v>1.7065</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0741</v>
+        <v>0.2323</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.339</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="9">
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. APARICIO RODRIGUEZ</t>
+          <t>F. DIAZ MARTINEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2906</v>
+        <v>-0.853</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2005</v>
+        <v>0.8266</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0901</v>
+        <v>-1.6796</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4807</v>
+        <v>-0.3213</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4742</v>
+        <v>-1.4316</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0066</v>
+        <v>1.1103</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0205</v>
+        <v>0.4731</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0205</v>
+        <v>-0.962</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.4351</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5013</v>
+        <v>-0.7945</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4947</v>
+        <v>-0.4696</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0066</v>
+        <v>-0.3248</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7789</v>
+        <v>1.5579</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1947</v>
+        <v>1.5579</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4204</v>
+        <v>-0.258</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2473</v>
+        <v>0.3535</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1731</v>
+        <v>-0.6115</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6105</v>
+        <v>-1.8316</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6105</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. DIAZ MARTINEZ</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4896</v>
+        <v>-2.0092</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7543</v>
+        <v>0.8333</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7353</v>
+        <v>-2.8425</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3213</v>
+        <v>-0.5239</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4316</v>
+        <v>-0.4429</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1103</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4731</v>
+        <v>1.4009</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.962</v>
+        <v>0.0873</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4351</v>
+        <v>1.3136</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7945</v>
+        <v>-1.9248</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4696</v>
+        <v>-0.5302</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3248</v>
+        <v>-1.3946</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5579</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5579</v>
+        <v>0.7789</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8946</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2275</v>
+        <v>0.4061</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6671</v>
+        <v>-0.4756</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8316</v>
+        <v>-1.2211</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8316</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>H. APARICIO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5396</v>
+        <v>-2.1515</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7745</v>
+        <v>-1.2005</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7651</v>
+        <v>-0.951</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7895</v>
+        <v>-0.4807</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5266</v>
+        <v>-0.4742</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2629</v>
+        <v>-0.0066</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4291</v>
+        <v>0.0205</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5977</v>
+        <v>0.0205</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8314</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3604</v>
+        <v>-0.5013</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-0.4947</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4315</v>
+        <v>-0.0066</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1947</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7789</v>
+        <v>0.1947</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1652</v>
+        <v>-0.2813</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1278</v>
+        <v>-0.2473</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0374</v>
+        <v>-0.0339</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2795</v>
+        <v>-0.6105</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5005</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2211</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,40 +1423,40 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7031</v>
+        <v>-2.837</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1116</v>
+        <v>-1.211</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8146</v>
+        <v>-1.626</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5239</v>
+        <v>-3.7895</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4429</v>
+        <v>-1.5266</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-2.2629</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4009</v>
+        <v>-2.4291</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0873</v>
+        <v>-0.5977</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3136</v>
+        <v>-1.8314</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9248</v>
+        <v>-1.3604</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5302</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3946</v>
+        <v>-0.4315</v>
       </c>
       <c r="P13" t="n">
         <v>-0.1947</v>
@@ -1468,19 +1468,19 @@
         <v>0.7789</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7634</v>
+        <v>0.8678</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3156</v>
+        <v>0.6913</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4477</v>
+        <v>0.1765</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2211</v>
+        <v>0.2795</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X13" t="n">
         <v>-1.2211</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9274</v>
+        <v>7.901199999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>14.7569</v>
+        <v>15.6842</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.8293</v>
+        <v>-7.782999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>5.230799999999998</v>
+        <v>5.230799999999999</v>
       </c>
       <c r="H14" t="n">
         <v>-4.7698</v>
@@ -1534,10 +1534,10 @@
         <v>-4.1571</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.413399999999999</v>
+        <v>-4.4134</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9736</v>
+        <v>-0.9735999999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.6843</v>
@@ -1546,16 +1546,16 @@
         <v>10.7104</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.066</v>
+        <v>-0.09229999999999994</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7385999999999996</v>
+        <v>1.6662</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.8044</v>
+        <v>-1.7582</v>
       </c>
       <c r="V14" t="n">
-        <v>3.736400000000001</v>
+        <v>3.7364</v>
       </c>
       <c r="W14" t="n">
         <v>11.9012</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8318</v>
+        <v>2.1162</v>
       </c>
       <c r="E15" t="n">
-        <v>7.1528</v>
+        <v>6.5548</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.321</v>
+        <v>-4.4386</v>
       </c>
       <c r="G15" t="n">
         <v>0.6882</v>
@@ -1624,13 +1624,13 @@
         <v>1.3632</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3909</v>
+        <v>0.6753</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8648</v>
+        <v>0.2668</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5261</v>
+        <v>0.4086</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6105</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. HETOR MENSAH</t>
+          <t>R. REID</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6415</v>
+        <v>1.8752</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8158</v>
+        <v>2.5785</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8257</v>
+        <v>-0.7033</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0237</v>
+        <v>0.718</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2566</v>
+        <v>2.4969</v>
       </c>
       <c r="I16" t="n">
-        <v>0.767</v>
+        <v>-1.7789</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2998</v>
+        <v>3.0955</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7723</v>
+        <v>2.689</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5275</v>
+        <v>0.4065</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7239</v>
+        <v>-2.3775</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4843</v>
+        <v>-0.192</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2396</v>
+        <v>-2.1855</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3895</v>
+        <v>0.1947</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9737</v>
+        <v>-1.9474</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5842000000000001</v>
+        <v>2.1421</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2351</v>
+        <v>0.0725</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1209</v>
+        <v>-0.0701</v>
       </c>
       <c r="U16" t="n">
-        <v>0.356</v>
+        <v>0.1426</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2279</v>
+        <v>0.89</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6105</v>
+        <v>1.5005</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8384</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. REID</t>
+          <t>M. HETOR MENSAH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.866</v>
+        <v>1.2411</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9805</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1145</v>
+        <v>0.6247</v>
       </c>
       <c r="G17" t="n">
-        <v>0.718</v>
+        <v>2.0237</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4969</v>
+        <v>1.2566</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7789</v>
+        <v>0.767</v>
       </c>
       <c r="J17" t="n">
-        <v>3.0955</v>
+        <v>1.2998</v>
       </c>
       <c r="K17" t="n">
-        <v>2.689</v>
+        <v>0.7723</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4065</v>
+        <v>0.5275</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3775</v>
+        <v>0.7239</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.192</v>
+        <v>0.4843</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.1855</v>
+        <v>0.2396</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1947</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9474</v>
+        <v>-0.9737</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1421</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9368</v>
+        <v>-0.1652</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6682</v>
+        <v>-0.3202</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2686</v>
+        <v>0.155</v>
       </c>
       <c r="V17" t="n">
-        <v>0.89</v>
+        <v>-0.2279</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5005</v>
+        <v>0.6105</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6105</v>
+        <v>-0.8384</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>L. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6734</v>
+        <v>0.4719</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5258</v>
+        <v>0.9966</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8524</v>
+        <v>-0.5248</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5812</v>
+        <v>-0.4653</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0479</v>
+        <v>-0.6548</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4666</v>
+        <v>0.1895</v>
       </c>
       <c r="J18" t="n">
-        <v>1.06</v>
+        <v>0.1715</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9623</v>
+        <v>-1.2469</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0978</v>
+        <v>1.4184</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4788</v>
+        <v>-0.6368</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0856</v>
+        <v>0.5921</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5644</v>
+        <v>-1.2289</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7789</v>
+        <v>0.9737</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7526</v>
+        <v>0.9737</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8653</v>
+        <v>0.5224</v>
       </c>
       <c r="T18" t="n">
-        <v>1.27</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4046</v>
+        <v>-0.3027</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.5521</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1695</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.7216</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3855</v>
+        <v>0.2423</v>
       </c>
       <c r="E19" t="n">
-        <v>3.3434</v>
+        <v>1.9278</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.9579</v>
+        <v>-1.6854</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0922</v>
+        <v>0.5812</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1524</v>
+        <v>1.0479</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0602</v>
+        <v>-0.4666</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9143</v>
+        <v>1.06</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9261</v>
+        <v>0.9623</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8404</v>
+        <v>0.0978</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0064</v>
+        <v>-0.4788</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7738</v>
+        <v>0.0856</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7802</v>
+        <v>-0.5644</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1947</v>
+        <v>0.7789</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1947</v>
+        <v>1.7526</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5624</v>
+        <v>0.4342</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2081</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.2377</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2795</v>
+        <v>-1.5521</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2211</v>
+        <v>1.1695</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5005</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. PANOS HUERTAS</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2143</v>
+        <v>0.1938</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1992</v>
+        <v>0.334</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4135</v>
+        <v>-0.1402</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4653</v>
+        <v>-0.6832</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6548</v>
+        <v>1.8324</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1895</v>
+        <v>-2.5156</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1715</v>
+        <v>1.1876</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2469</v>
+        <v>1.7705</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4184</v>
+        <v>-0.5828</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6368</v>
+        <v>-1.8708</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5921</v>
+        <v>0.062</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2289</v>
+        <v>-1.9328</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9737</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9737</v>
+        <v>1.7526</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1637</v>
+        <v>-0.201</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0277</v>
+        <v>-0.1273</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1914</v>
+        <v>-0.0736</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5590000000000001</v>
+        <v>1.2726</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.477</v>
+        <v>-0.068</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.06469999999999999</v>
+        <v>2.6457</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4123</v>
+        <v>-2.7137</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6832</v>
+        <v>-0.0922</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8324</v>
+        <v>-0.1524</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.5156</v>
+        <v>0.0602</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1876</v>
+        <v>0.9143</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7705</v>
+        <v>-0.9261</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5828</v>
+        <v>1.8404</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8708</v>
+        <v>-1.0064</v>
       </c>
       <c r="N21" t="n">
-        <v>0.062</v>
+        <v>0.7738</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9328</v>
+        <v>-1.7802</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1947</v>
+        <v>0.1947</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7526</v>
+        <v>0.1947</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8717</v>
+        <v>0.1089</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.526</v>
+        <v>0.5104</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3457</v>
+        <v>-0.4015</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2726</v>
+        <v>-0.2795</v>
       </c>
       <c r="W21" t="n">
         <v>1.2211</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0516</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="22">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5366</v>
+        <v>-1.5923</v>
       </c>
       <c r="E23" t="n">
         <v>-1.8253</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2887</v>
+        <v>0.233</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6187</v>
@@ -2248,13 +2248,13 @@
         <v>0.9737</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3616</v>
+        <v>0.306</v>
       </c>
       <c r="T23" t="n">
         <v>0.3553</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0063</v>
+        <v>-0.0494</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2795</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.991</v>
+        <v>-3.5528</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9877</v>
+        <v>-3.6887</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0033</v>
+        <v>0.1358</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6062</v>
@@ -2326,13 +2326,13 @@
         <v>0.9737</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4112</v>
+        <v>0.027</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5473</v>
+        <v>-0.2483</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1361</v>
+        <v>0.2753</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.5777</v>
+        <v>-6.6612</v>
       </c>
       <c r="E25" t="n">
         <v>-0.9657</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.612</v>
+        <v>-5.6955</v>
       </c>
       <c r="G25" t="n">
         <v>-3.371</v>
@@ -2404,13 +2404,13 @@
         <v>0.9737</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1575</v>
+        <v>0.0741</v>
       </c>
       <c r="T25" t="n">
         <v>0.0646</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0929</v>
+        <v>0.0095</v>
       </c>
       <c r="V25" t="n">
         <v>-2.3905</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.927299999999999</v>
+        <v>-6.262700000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>9.0504</v>
+        <v>9.050400000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>-15.9778</v>
+        <v>-15.3133</v>
       </c>
       <c r="G26" t="n">
         <v>-5.2308</v>
@@ -2461,13 +2461,13 @@
         <v>4.1574</v>
       </c>
       <c r="L26" t="n">
-        <v>4.413600000000001</v>
+        <v>4.413599999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-13.8013</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6124999999999998</v>
+        <v>0.6125000000000003</v>
       </c>
       <c r="O26" t="n">
         <v>-14.4138</v>
@@ -2482,13 +2482,13 @@
         <v>11.6842</v>
       </c>
       <c r="S26" t="n">
-        <v>1.0657</v>
+        <v>1.7305</v>
       </c>
       <c r="T26" t="n">
-        <v>1.8044</v>
+        <v>1.8045</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7386000000000001</v>
+        <v>-0.07390000000000015</v>
       </c>
       <c r="V26" t="n">
         <v>-3.7364</v>
